--- a/校园招聘/制造业/消费电子／通信／智能设备/技术研发类/电气工程师/3_需重新出题/4轮_消费电子／通信／智能设备_电气工程师_需要重新出题.xlsx
+++ b/校园招聘/制造业/消费电子／通信／智能设备/技术研发类/电气工程师/3_需重新出题/4轮_消费电子／通信／智能设备_电气工程师_需要重新出题.xlsx
@@ -1,38 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chengxi5\Desktop\8月AI审题\消费电子通信智能设备\电气工程师\4轮审核后需要重出的内容\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/risei/Desktop/北森-测评产品经理/AI面试官/专业能力/8月迭代/出题表格/知识审核/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4B4C35-5278-F344-8A63-7DD5DF6CE99A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="5530"/>
+    <workbookView xWindow="620" yWindow="860" windowWidth="19140" windowHeight="16480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="出题" sheetId="1" r:id="rId1"/>
+    <sheet name="出答案" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
   <si>
     <t>问题</t>
   </si>
   <si>
-    <t>第一层</t>
-  </si>
-  <si>
-    <t>第二层</t>
-  </si>
-  <si>
-    <t>第三层</t>
-  </si>
-  <si>
     <t>技能分类</t>
   </si>
   <si>
@@ -63,15 +56,6 @@
     <t>请简单说说电压串联负反馈对放大器输入电阻和输出电阻的影响。</t>
   </si>
   <si>
-    <t>电压串联负反馈会使放大器的输入电阻增大，输出电阻减小。这是由反馈信号的取样方式和比较方式共同决定的：因为反馈信号从输出电压中取出，并与输入信号以串联方式叠加，所以输入端呈现更高阻抗；同时，反馈网络试图稳定输出电压，使输出端对外部负载变化的响应更弱，表现为输出电阻下降。</t>
-  </si>
-  <si>
-    <t>在消费电子和智能设备硬件开发中，工程师常通过运放电路实现电压串联负反馈结构，比如仪表放大器前端、ADC驱动电路或高精度传感器信号调理模块。常见实现方案有三种：一是采用分立电阻网络加通用运放搭建，成本低但温漂和匹配性受限；二是选用集成式精密仪表放大器，内置匹配电阻且温漂控制好，适合中高端产品；三是用带内部反馈路径的可编程增益放大器，支持动态配置但需关注数字接口引入的噪声耦合风险。综合来看，集成式仪表放大器方案在量产一致性、调试效率和长期可靠性上优势最明显，尤其适配校招工程师快速上手和量产导入阶段的稳定性要求。</t>
-  </si>
-  <si>
-    <t>1个异常情况概要：输入电阻未达预期导致前级传感器信号衰减。具体情况：某温湿度传感器输出内阻较高，接入采用电压串联负反馈的运放电路后，实测信号幅度偏低，排查发现反馈电阻网络布局靠近高频干扰源，引起共模抑制比劣化，等效削弱了串联反馈对输入阻抗的提升效果。解决思路：重新规划敏感模拟走线，将反馈电阻就近放置于运放同相输入端附近，并增加输入端RC滤波以抑制高频耦合。1个复杂问题概要：输出电阻降低不足引发负载调整率超标。具体问题：在为MCU供电的LDO后级增加电压串联负反馈缓冲电路时，带载后输出电压随电流变化超出规格要求，根源是运放输出级驱动能力与反馈环路相位裕度不匹配，导致闭环输出阻抗在动态负载下回升。解决思路：在反馈网络中引入零点补偿电容优化环路响应，同时评估运放输出摆率与负载电容的兼容性，必要时改用轨到轨输出且驱动能力强的型号。</t>
-  </si>
-  <si>
     <t>电路基础</t>
   </si>
   <si>
@@ -94,15 +78,6 @@
   </si>
   <si>
     <t>在绘制原理图时，当同一张图纸中存在多个不同电压等级的电源网络（比如3.3V、5V、12V）和多个地网络（如数字地、模拟地、屏蔽地），请简述如何通过网络标注方式清晰区分它们，避免混淆或误连。</t>
-  </si>
-  <si>
-    <t>应为每类电源和地网络设置唯一、语义明确、带前缀或后缀标识的网络标号，例如3V3_DIG、5V_SYS、12V_PWR；数字地用GND_DIG、模拟地用GND_ANA、屏蔽地用GND_SHLD，并确保同一物理网络在全图中使用完全一致的标号，禁止混用缩写、大小写变体或同义别名。</t>
-  </si>
-  <si>
-    <t>当前主流做法有四种：一是纯文本命名法，即按功能+层级+类型组合命名，优点是直观可读、便于评审追溯，缺点是依赖工程师规范意识，易出现拼写不一致；二是符号+文本双标注法，在网络标号旁叠加标准化电源/地图形符号，增强视觉识别，但需统一符号库且增加绘图时间；三是分页分区命名法，将不同电压域和地域划分到独立原理图页并加页头说明，适合复杂系统，但跨页连接易遗漏标注；四是EDA工具约束驱动法，利用最新版设计软件的网络分类规则和电气规则检查功能，自动校验标号唯一性与连接合规性。综合来看，纯文本命名法配合工具规则检查是最优组合，兼顾效率、可维护性与量产协同要求。</t>
-  </si>
-  <si>
-    <t>1个异常情况概要：同一张原理图中出现GND和GND_DIG被误标为同一网络。具体情况：工程师未注意默认地符号的全局属性，导致数字地与系统地意外短接，引发模拟电路噪声超标。解决思路：建立地网络命名强制检查清单，在原理图评审阶段逐项核对所有地标号是否带功能后缀，并启用EDA工具的地网络隔离规则预警。1个复杂问题概要：多电源域交叉供电场景下标号逻辑与实际物理隔离矛盾。具体问题：某通信模块同时接入3V3_DIG和3V3_ANA，但原理图仅用3V3标注，未体现供电路径隔离意图，PCB布线时误将两类3.3V走线共用铜皮。解决思路：在电源标号中嵌入供电路径标识，如3V3_DIG_FROM_LDO1、3V3_ANA_FROM_DCDC2，并在对应电源器件旁添加供电路径注释框，确保原理图能直接支撑后续PCB分区布局与电源完整性分析。</t>
   </si>
   <si>
     <t>电气原理图设计</t>
@@ -123,13 +98,147 @@
   <si>
     <t>重出答案时采用“可口语复述三层结构”模板：第一层给定义与边界，第二层给常见方案比较与适用条件，第三层给1个高频异常+1个复杂约束及排查步骤。每层避免绝对化表述，关键参数必须注明前提条件与适用范围；并明确区分终端板级与适配器侧职责边界，防止把偏门场景继续写进答案导致B1/B5复发。</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电气：
+一、岗位通用职责
+1. 硬件方案设计与原理图输出
+根据产品需求完成电气/硬件方案设计、原理图绘制、模块电路设计与技术评审；校招/初级侧重读图、绘制常规电路原理图和协助方案整理，1-3年侧重独立完成模块电路设计，3-5年侧重整机硬件架构定义、指标分解与方案评审。
+2. 电路原理分析与器件选型
+理解供电、信号链、接口、保护等电路的工作原理、信号流向与关键参数，完成电子元器件选型、Datasheet 评估与 BOM 输出；校招/初级侧重识别主要电路模块与基础器件参数，1-3年侧重按电路原理判断异常来源并完成常规选型，3-5年侧重从原理层面分析瓶颈、故障根因与降本替代方向。
+3. 样机调试、测试与故障定位
+参与新产品、改版样机及试产板的上电、功能调试、性能测试和问题定位与优化；校招/初级侧重协助焊接、调试与测试记录，1-3年侧重独立处理常见硬件问题，3-5年侧重制定调试方案、疑难/偶发问题根因分析和整改闭环。
+4. 设计文档与硬件技术档案管理
+建立并维护原理图/PCB 资料、BOM 清单、器件归一化清单、设计文档、测试规范与版本履历，根据问题频率与器件关键度优化选型与替代策略，支撑研发协同与量产追溯。
+二、方向职责
+方向一：电源与电路设计方向
+1. 完成产品供电方案、开关电源拓扑设计、控制环路与功率/磁性器件选型，满足效率、纹波、温升等指标。
+2. 进行电源指标优化、低功耗与电源管理设计，处理量产中的电源相关问题。
+方向二：PCB与信号完整性方向
+1. 完成 PCB 布局布线、叠层与阻抗控制、高速接口设计与信号/电源完整性处理。
+2. 推进可制造性设计与生产文件输出，配合解决 SI/PI 及布线相关问题。
+方向三：机电接口与系统集成方向
+1. 完成 MCU/SoC 最小系统、通信接口、通信模组/射频天线、传感器与连接器等接口设计。
+2. 推进软硬件联调与系统集成，配合解决接口兼容与系统级问题。
+方向四：EMC、认证与可靠性方向
+1. 完成 EMC/EMI 预测试与整改、ESD 与防护设计、安规与认证测试（CE/FCC/3C/UL）。
+2. 推进环境可靠性试验、降额与稳健设计，确保产品满足国内外标准与可靠性要求。
+方向五：调试验证与量产导入方向
+1. 跟进样机功能验证、性能测试，制定测试规范与测试方案。
+2. 推进试产与量产导入（NPI），完成量产不良根因分析与整改闭环。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"你是一位经验丰富的资深面试官，拥有超过 10 年人才招聘经验。你尤其擅长从知识深度、逻辑思维以及实战能力等多个维度全面评估候选人。
+现在请依据以下要求，为【{{industry}}】行业下的【{{job}}】岗位的候选人精心准备【{{num}}】道视频面试题。
+关于目标行业下岗位的岗位描述：【{{JD}}】
+## 面试题要求
+- 题目类型：必须为简答题。
+- 内容相关性：题目内容要紧密围绕【{{category}}】技能分类下【{{skill}}】技能里的【{{knowledge}}】知识点展开。
+- 行业岗位适用性：题目需与【{{industry}}】行业下的【{{job}}】岗位职责高度适配，贴合该行业实际情况。
+- 招聘场景：题目应契合【{{scene}}】这一特定招聘场景。
+- 题目难度：全部设定为【{{level}}】难度，具体难度定义如下：
+    · 简单：考察应聘者能否识别、回忆出关键概念，是否了解关键概念背后的基本原理。提问需从小而具体的切入点考察对某知识点的概念识别与规则理解，无场景，纯理论考察。如“请简述什么是负载均衡技术中轮询策略”。建议作答时间控制在60秒内。字数控制在10～30字。
+    · 中等：考察应聘者是否知道在一个简单应用场景下用何种方法解决问题，解决机制是什么。提问内容涉及概念与规则的基础应用，场景是这个知识点常见的简单应用场景，禁止涉及穷举、优劣势分析、系统性设计或冲突情况。如“当一个服务有多个实例时，负载均衡器是怎么判断某个实例‘可用’从而把请求转发过去的？”建议作答时间控制在90秒内。字数控制在30～60字。
+    · 困难：考察应聘者是否知道在复杂/业务场景下如何运用知识点进行系统设计或优化来解决问题。提问内容涉及通过多规则整合进行复杂问题解决，需要候选人分析多方面的因素，权衡不同的选择，提出解决方案，并清晰阐述决策的依据和逻辑。场景应是较为复杂的业务场景。如“线上服务在高峰期出现部分用户延迟很高，但监控显示整体 CPU 并不高，你怀疑是负载均衡分配不均导致的。你会如何定位问题，并调整负载均衡策略来改善长尾延迟？” 。建议作答时间控制在120秒内。字数控制在60～90字。
+- 题干长度：一个题目里只能有1个小问，禁止连环提问！使读题时间控制在30秒内，难度越低的题题干应越好理解。
+-易答性：
+1.禁用词：写代码、写出、编写、绘制、计算等一些口头无法表述的内容，确保候选人仅通过口头回答即可完成答题；
+2.不能出现让候选人讲述某一个软件的操作步骤；
+3.提问应该逻辑严谨，简单易懂，提出问题时需要模仿面试官在面试的口吻，不能过于生硬而让候选人不能明白题目的意思；
+4.编程题要给出规定的编程语言。
+- 内容限制：
+1.问题中的应用场景/条件不能是虚构的或者故事化的场景。语言上，类似“假设....”的提问是不被允许的。
+2.技术时效性：题干禁止问旧版本/早期版本的技术，涉及的技术场景必须是2022年之后在用的，但不必在题干中标注年份。
+3.问题中不能出现【{{industry}}】行业名称、【{{scene}}】特定招聘场景名称、【{{job}}】职位
+4.对于【通用行业】的知识点提问需要通用化，业务场景需要是各行各业的应聘者都能看懂的。
+5.所有的问题都是知识点面试问题，不能出行为化面试题
+6.尽量不要出现英文，能用中文的用中文表达！
+7.禁止出现事实、知识错误！
+8.禁止出现“请用一句话回答”这类强势粗暴的提问方法，可以说“请简述”“请简单说说”等
+## 输出规范要求
+- 若题目数量超过 1 道，要保证所有题目内容不重复，从不同主题或提问角度进行设计。
+- 严格以规范的 JSON 格式输出结果，不包含任何额外的文本说明。
+## 输出示例
+{{
+    ""questions"": [{{
+        ""question"": ""题目题干""，
+        ""level"": ""难度"",
+        ""time"": 建议答题时间，整数类型
+    }}]
+}}"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"电气：
+一、岗位通用职责
+1. 硬件方案设计与原理图输出
+根据产品需求完成电气/硬件方案设计、原理图绘制、模块电路设计与技术评审；校招/初级侧重读图、绘制常规电路原理图和协助方案整理，1-3年侧重独立完成模块电路设计，3-5年侧重整机硬件架构定义、指标分解与方案评审。
+2. 电路原理分析与器件选型
+理解供电、信号链、接口、保护等电路的工作原理、信号流向与关键参数，完成电子元器件选型、Datasheet 评估与 BOM 输出；校招/初级侧重识别主要电路模块与基础器件参数，1-3年侧重按电路原理判断异常来源并完成常规选型，3-5年侧重从原理层面分析瓶颈、故障根因与降本替代方向。
+3. 样机调试、测试与故障定位
+参与新产品、改版样机及试产板的上电、功能调试、性能测试和问题定位与优化；校招/初级侧重协助焊接、调试与测试记录，1-3年侧重独立处理常见硬件问题，3-5年侧重制定调试方案、疑难/偶发问题根因分析和整改闭环。
+4. 设计文档与硬件技术档案管理
+建立并维护原理图/PCB 资料、BOM 清单、器件归一化清单、设计文档、测试规范与版本履历，根据问题频率与器件关键度优化选型与替代策略，支撑研发协同与量产追溯。
+二、方向职责
+方向一：电源与电路设计方向
+1. 完成产品供电方案、开关电源拓扑设计、控制环路与功率/磁性器件选型，满足效率、纹波、温升等指标。
+2. 进行电源指标优化、低功耗与电源管理设计，处理量产中的电源相关问题。
+方向二：PCB与信号完整性方向
+1. 完成 PCB 布局布线、叠层与阻抗控制、高速接口设计与信号/电源完整性处理。
+2. 推进可制造性设计与生产文件输出，配合解决 SI/PI 及布线相关问题。
+方向三：机电接口与系统集成方向
+1. 完成 MCU/SoC 最小系统、通信接口、通信模组/射频天线、传感器与连接器等接口设计。
+2. 推进软硬件联调与系统集成，配合解决接口兼容与系统级问题。
+方向四：EMC、认证与可靠性方向
+1. 完成 EMC/EMI 预测试与整改、ESD 与防护设计、安规与认证测试（CE/FCC/3C/UL）。
+2. 推进环境可靠性试验、降额与稳健设计，确保产品满足国内外标准与可靠性要求。
+方向五：调试验证与量产导入方向
+1. 跟进样机功能验证、性能测试，制定测试规范与测试方案。
+2. 推进试产与量产导入（NPI），完成量产不良根因分析与整改闭环。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你是一位经验丰富的资深面试官，拥有超过 10 年人才招聘经验。你尤其擅长从知识深度、逻辑思维以及实战能力等多个维度全面评估候选人。
+现在请依据以下要求，为面试【{{job}}】职位的候选人的视频面试题【{{Q}}】生成符合规则的参考答案。
+## 参考答案要求
+- 内容相关性：题目内容要紧密围绕【{{category}}】技能分类下【{{skill}}】技能里的【{{knowledge}}】知识点展开。
+- 岗位适用性：答案需与【{{{industry}}】行业的【{{job}}】岗位的工作范畴高度适配，仅从该岗位工作内容角度生成。禁止从技术的口径回答问题！！岗位工作内容参考：【{{JD}}】
+- 使用场景：答案应契合【{{scene}}】这一特定使用场景。
+- 内容与格式：每个题目的三层参考答案字数合计限制在300～600字，每个题目考察的都是一个岗位上某个技能的掌握程度，掌握程度分为以下三个层次，因此参考答案也需要分层生成。对第一层给出回答题干所需的基础知识，内容严格对应题干，不要举例，不要超出题干所问的范围！对第二层给出这个应用场景下常见的2～4种技术方案或方法的分析，优劣势分别是什么，哪种最好，方法要在保证时效性的基础上全面！分析要深入！对第三层给出这个知识点或场景下最最常出现的1个异常情况和1个复杂问题，以及每种情况的解决思路，输出时要结构化！小标题结构为：1个异常情况概要，具体情况，解决思路；1个复杂问题概要，具体问题，解决思路。
+参考答案约束：
+1.参考答案的内容必须严格对应岗位口径
+2.禁止出现代码块、符号等书面表达，所有类似内容必须用口语自然语言描述的形式代替
+3.禁止出现公式、计算等
+4.能用中文的用中文表达
+5.涉及的技术方法必须是2023年之后在用的，但相关时间信息不必出现在答案文本中
+6.禁止出现知识、事实错误！！
+常见的错误清单：{把相近概念混为一谈
+把局部实现写成通用规律
+把适用条件说错或漏掉前提
+把可选方案写成唯一答案
+数学/统计结论直接上升为业务结论
+边界值、分类、覆盖率类题目只答一半
+举例本身错误
+绝对化、法条化、一刀切表述
+业务场景包装过重，压坏技术口径}
+## 输出示例
+{{
+    "questions": [{{
+        "question": "题目题干"，
+        "answer1":"参考答案-第一层",
+        "answer2":"参考答案-第二层",
+        "answer3":"参考答案-第三层"
+    }}]
+}}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,6 +250,21 @@
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="4"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -165,8 +289,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -468,11 +601,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -503,90 +636,72 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+    </row>
+    <row r="2" spans="1:11" ht="409.6">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
+      <c r="I2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="K2" t="s">
         <v>23</v>
       </c>
-      <c r="N2" t="s">
-        <v>32</v>
-      </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="409.6">
       <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" t="s">
         <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -594,4 +709,31 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18716F96-9E52-D142-B7A7-8FDA92687D3A}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="409.6">
+      <c r="A2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>